--- a/sampleprojects/TaxReturn/excel/states/MA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MA.xlsx
@@ -84,7 +84,7 @@
     <t>MFJ/QSS: exemption $8,800; tax = max(AGI − 8,800, 0) × 5.00% + surtax</t>
   </si>
   <si>
-    <t>set result.ma_taxable_income = the maximum of (result.agi - 8800.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
+    <t>set result.ma_taxable_income = the maximum of (result.state_calc_agi - 8800.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
   </si>
   <si>
     <t>X</t>
@@ -93,13 +93,13 @@
     <t>HOH: exemption $6,800; tax = max(AGI − 6,800, 0) × 5.00% + surtax</t>
   </si>
   <si>
-    <t>set result.ma_taxable_income = the maximum of (result.agi - 6800.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
+    <t>set result.ma_taxable_income = the maximum of (result.state_calc_agi - 6800.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
   </si>
   <si>
     <t>Default (Single/MFS): exemption $4,400; tax = max(AGI − 4,400, 0) × 5.00% + surtax</t>
   </si>
   <si>
-    <t>set result.ma_taxable_income = the maximum of (result.agi - 4400.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
+    <t>set result.ma_taxable_income = the maximum of (result.state_calc_agi - 4400.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>

--- a/sampleprojects/TaxReturn/excel/states/MA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MA.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="MA Tax" sheetId="2" r:id="rId4"/>
     <sheet name="MA Military Retirement Exclusio" sheetId="3" r:id="rId6"/>
-    <sheet name="EDD" sheetId="4" r:id="rId7"/>
+    <sheet name="MA Exemption Ratio" sheetId="4" r:id="rId7"/>
+    <sheet name="EDD" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>DT: MA Tax</t>
   </si>
@@ -48,6 +49,9 @@
     <t>set result.ma_state_tax = 0; set result.ma_taxable_income = 0; set result.ma_surtax = 0; add "  Massachusetts Tax Calculation (Form 1) - flat 5.00% + 4% surtax over $1,083,150" to job.audit_trail</t>
   </si>
   <si>
+    <t>perform MA_Exemption_Ratio</t>
+  </si>
+  <si>
     <t>CONDITIONS: COMMENTS</t>
   </si>
   <si>
@@ -81,25 +85,25 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>MFJ/QSS: exemption $8,800; tax = max(AGI − 8,800, 0) × 5.00% + surtax</t>
-  </si>
-  <si>
-    <t>set result.ma_taxable_income = the maximum of (result.state_calc_agi - 8800.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
+    <t>Form 1-NR/PY line 4a 8,800 married filing jointly / qualifying surviving spouse exemption plus line 4b $1,000 per dependent claimed on the U.S. return (every dependent on the return); line 22 multiplies the total (22a) by the ratio; line 23 = max(21 - 22, 0); line 26 = 5.0% of line 23 (2025 Form 1-NR/PY)</t>
+  </si>
+  <si>
+    <t>set result.ma_total_exemptions = 8800.0 + result.ma_exemption_dependent * (double) (length of job.dependents); set result.ma_taxable_income = the maximum of (result.state_calc_agi - result.ma_total_exemptions * result.ma_exemption_ratio) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05; add "  MA exemptions (line 4g): $8,800 married filing jointly / qualifying surviving spouse + " + (length of job.dependents) + " dependents x $1,000 = $" + result.ma_total_exemptions + "; line 22: x " + result.ma_exemption_ratio + " = $" + (result.ma_total_exemptions * result.ma_exemption_ratio) + "; 5.0% income after exemptions (line 23): $" + result.ma_taxable_income to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>HOH: exemption $6,800; tax = max(AGI − 6,800, 0) × 5.00% + surtax</t>
-  </si>
-  <si>
-    <t>set result.ma_taxable_income = the maximum of (result.state_calc_agi - 6800.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
-  </si>
-  <si>
-    <t>Default (Single/MFS): exemption $4,400; tax = max(AGI − 4,400, 0) × 5.00% + surtax</t>
-  </si>
-  <si>
-    <t>set result.ma_taxable_income = the maximum of (result.state_calc_agi - 4400.0) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05</t>
+    <t>Form 1-NR/PY line 4a 6,800 head of household exemption plus line 4b $1,000 per dependent claimed on the U.S. return (every dependent on the return); line 22 multiplies the total (22a) by the ratio; line 23 = max(21 - 22, 0); line 26 = 5.0% of line 23 (2025 Form 1-NR/PY)</t>
+  </si>
+  <si>
+    <t>set result.ma_total_exemptions = 6800.0 + result.ma_exemption_dependent * (double) (length of job.dependents); set result.ma_taxable_income = the maximum of (result.state_calc_agi - result.ma_total_exemptions * result.ma_exemption_ratio) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05; add "  MA exemptions (line 4g): $6,800 head of household + " + (length of job.dependents) + " dependents x $1,000 = $" + result.ma_total_exemptions + "; line 22: x " + result.ma_exemption_ratio + " = $" + (result.ma_total_exemptions * result.ma_exemption_ratio) + "; 5.0% income after exemptions (line 23): $" + result.ma_taxable_income to job.audit_trail</t>
+  </si>
+  <si>
+    <t>Form 1-NR/PY line 4a 4,400 single / married filing separately exemption plus line 4b $1,000 per dependent claimed on the U.S. return (every dependent on the return); line 22 multiplies the total (22a) by the ratio; line 23 = max(21 - 22, 0); line 26 = 5.0% of line 23 (2025 Form 1-NR/PY)</t>
+  </si>
+  <si>
+    <t>set result.ma_total_exemptions = 4400.0 + result.ma_exemption_dependent * (double) (length of job.dependents); set result.ma_taxable_income = the maximum of (result.state_calc_agi - result.ma_total_exemptions * result.ma_exemption_ratio) and 0.0; set result.ma_state_tax = result.ma_taxable_income * 0.05; add "  MA exemptions (line 4g): $4,400 single / married filing separately + " + (length of job.dependents) + " dependents x $1,000 = $" + result.ma_total_exemptions + "; line 22: x " + result.ma_exemption_ratio + " = $" + (result.ma_total_exemptions * result.ma_exemption_ratio) + "; 5.0% income after exemptions (line 23): $" + result.ma_taxable_income to job.audit_trail</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -132,6 +136,45 @@
     <t>TABLE_NUMBER: 42101</t>
   </si>
   <si>
+    <t>DT: MA Exemption Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 42102</t>
+  </si>
+  <si>
+    <t>The roster entry being computed is a non-resident of Massachusetts. Form 1-NR/PY line 22: nonresidents multiply line 22a by line 14g (income ratio); part-year residents multiply by line 3 (days as a resident, column 2); a full-year resident takes the whole exemption (column 3)</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "nonresident"</t>
+  </si>
+  <si>
+    <t>A part-year resident entry: Form 1-NR/PY lines 2 and 3 prorate the exemption by days of residence, not by income</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "part_year"</t>
+  </si>
+  <si>
+    <t>2025 Form 1-NR/PY line 14g: divide line 14d (Massachusetts-source income) by line 14f (total income this return = 14d + 14e), carried to four decimal places. 14e is non-Massachusetts income, not less than 0 (form), from total U.S. income before adjustments (Form 1040 line 9) less what Massachusetts does not tax; Social Security and state tax refunds are the exclusions the engine models (see result.ma_non_ma_income). The Social Security term subtracts the whole benefit because the federal pass (Calculate_SS_Taxability) includes the whole benefit in gross_income; when the federal pass is corrected, subtract result.taxable_social_security instead -- scenario MultiState_19 holds the Massachusetts figure ($1,423.26) either way and will say so. Not federal AGI: the review of #1328 showed a $7,000 IRA deduction moving the ratio from 0.25 to 0.2655 when AGI was the denominator. The cap at 1.0 follows from 14e &gt;= 0</t>
+  </si>
+  <si>
+    <t>set result.ma_non_ma_income = the maximum of (result.gross_income - result.total_social_security - result.state_tax_refund - result.state_calc_agi) and 0.0; set result.ma_total_income = result.state_calc_agi + result.ma_non_ma_income; set result.ma_exemption_ratio = (result.state_calc_agi / result.ma_total_income) rounded to 4 decimal places; add "  MA deduction and exemption ratio (Form 1-NR/PY line 14g): Massachusetts income $" + result.state_calc_agi + " (14d) / total income this return $" + result.ma_total_income + " (14f = 14d + non-Massachusetts income $" + result.ma_non_ma_income + " (14e)) = " + result.ma_exemption_ratio to job.audit_trail</t>
+  </si>
+  <si>
+    <t>A full-year resident takes the whole exemption (Form 1, line 22 has no ratio)</t>
+  </si>
+  <si>
+    <t>set result.ma_exemption_ratio = 1.0</t>
+  </si>
+  <si>
+    <t>Line 3: total days as a Massachusetts resident divided by 365, carried to four decimal places (2025 Form 1-NR/PY instructions, Lines 2 and 3). The days come from the roster entry period (state_tax_result.days_in_state, both ends counted), published as result.state_calc_days_in_state</t>
+  </si>
+  <si>
+    <t>set result.ma_exemption_ratio = ((double) result.state_calc_days_in_state / 365.0) rounded to 4 decimal places; add "  MA exemption ratio (Form 1-NR/PY line 3): " + result.state_calc_days_in_state + " days resident / 365 = " + result.ma_exemption_ratio to job.audit_trail</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -177,7 +220,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(13 attributes)</t>
+    <t>(17 attributes)</t>
   </si>
   <si>
     <t>ma_exemption_age_65</t>
@@ -231,6 +274,18 @@
     <t>MA personal exemption married filing jointly (2025)</t>
   </si>
   <si>
+    <t>ma_exemption_ratio</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>The factor Form 1-NR/PY line 22 multiplies the exemptions (line 22a) by, carried to four decimal places as the instructions require: for a nonresident entry line 14g, Massachusetts-source income (14d) over total income this return (14f = 14d + 14e, result.ma_total_income) -- at most 1.0 because 14e is not less than 0; for a part_year entry line 3, days as a Massachusetts resident over 365; 1.0 for a full-year resident. Set by MA_Exemption_Ratio (#1201).</t>
+  </si>
+  <si>
     <t>ma_exemption_single</t>
   </si>
   <si>
@@ -249,15 +304,21 @@
     <t>MA minimum income threshold for taxation (2025)</t>
   </si>
   <si>
+    <t>ma_non_ma_income</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Form 1-NR/PY line 14e, non-Massachusetts source income, not less than 0: the income that would have been reported had the taxpayer been a resident, from total U.S. income (Form 1040 line 9) less what Massachusetts does not tax. The engine models two of the exclusions the instructions list: Social Security and state tax refunds (result.state_tax_refund). The Social Security term is result.total_social_security, the whole benefit, because Calculate_SS_Taxability puts the whole benefit into gross_income and AGI; when that is corrected to the taxable part, this term must become result.taxable_social_security, and scenario MultiState_19 (which asserts the Massachusetts tax, not the federal AGI) will fail until it does. Not modelled, no field: U.S. bond interest, contributory government pensions, Keogh and 403(b) distributions already taxed by Massachusetts, the add-back of other states bond interest, Massachusetts public employees pension contributions; the foreign earned income and NOL add-backs do not arise because the engine never excludes the former from gross_income and takes the latter below AGI. Computed as gross_income - total_social_security - state_tax_refund - Massachusetts-source income, floored at 0, by MA_Exemption_Ratio (#1201).</t>
+  </si>
+  <si>
     <t>ma_state_tax</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>rw</t>
-  </si>
-  <si>
     <t>MA state income tax (regular + surtax)</t>
   </si>
   <si>
@@ -298,6 +359,18 @@
   </si>
   <si>
     <t>MA taxable income (AGI minus filing-status exemption)</t>
+  </si>
+  <si>
+    <t>ma_total_exemptions</t>
+  </si>
+  <si>
+    <t>Form 1-NR/PY line 4g / 22a, total exemptions before proration: the filing-status personal exemption (line 4a: $4,400 single or MFS, $6,800 HOH, $8,800 MFJ) plus $1,000 per dependent (line 4b, result.ma_exemption_dependent x the dependents on the return). Age 65 and blindness exemptions (4c, 4d) are not modelled. Set by MA_Tax (#1201).</t>
+  </si>
+  <si>
+    <t>ma_total_income</t>
+  </si>
+  <si>
+    <t>Form 1-NR/PY line 14f, total income this return: line 14d (Massachusetts-source income, result.state_calc_agi) plus line 14e (result.ma_non_ma_income). The denominator of the line 14g ratio; not federal AGI, which differs by the adjustments to income and by what Massachusetts excludes (#1201).</t>
   </si>
 </sst>
 </file>
@@ -920,312 +993,280 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+    <row r="10">
+      <c r="A10" s="5">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="1">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" s="1">
         <v>4</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H12" s="1">
         <v>5</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I12" s="1">
         <v>6</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J12" s="1">
         <v>7</v>
       </c>
-      <c r="K11" s="1">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="K12" s="1">
+        <v>8</v>
+      </c>
+      <c r="L12" s="1">
         <v>9</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M12" s="1">
         <v>10</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N12" s="1">
         <v>11</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O12" s="1">
         <v>12</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P12" s="1">
         <v>13</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q12" s="1">
         <v>14</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R12" s="1">
         <v>15</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S12" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>11</v>
+      </c>
+      <c r="O16" s="4">
+        <v>12</v>
+      </c>
+      <c r="P16" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="4">
         <v>14</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="R16" s="4">
         <v>15</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2</v>
-      </c>
-      <c r="F15" s="4">
-        <v>3</v>
-      </c>
-      <c r="G15" s="4">
-        <v>4</v>
-      </c>
-      <c r="H15" s="4">
-        <v>5</v>
-      </c>
-      <c r="I15" s="4">
-        <v>6</v>
-      </c>
-      <c r="J15" s="4">
-        <v>7</v>
-      </c>
-      <c r="K15" s="4">
-        <v>8</v>
-      </c>
-      <c r="L15" s="4">
-        <v>9</v>
-      </c>
-      <c r="M15" s="4">
-        <v>10</v>
-      </c>
-      <c r="N15" s="4">
-        <v>11</v>
-      </c>
-      <c r="O15" s="4">
-        <v>12</v>
-      </c>
-      <c r="P15" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>14</v>
-      </c>
-      <c r="R15" s="4">
-        <v>15</v>
-      </c>
-      <c r="S15" s="4">
+      <c r="S16" s="4">
         <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -1272,22 +1313,22 @@
     </row>
     <row r="18">
       <c r="A18" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -1331,182 +1372,182 @@
     </row>
     <row r="19">
       <c r="A19" s="5">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>4</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
+      <c r="D20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="1">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="1">
         <v>1</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F22" s="1">
         <v>3</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G22" s="1">
         <v>4</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H22" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I22" s="1">
         <v>6</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J22" s="1">
         <v>7</v>
       </c>
-      <c r="K21" s="1">
-        <v>8</v>
-      </c>
-      <c r="L21" s="1">
+      <c r="K22" s="1">
+        <v>8</v>
+      </c>
+      <c r="L22" s="1">
         <v>9</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M22" s="1">
         <v>10</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N22" s="1">
         <v>11</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O22" s="1">
         <v>12</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P22" s="1">
         <v>13</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q22" s="1">
         <v>14</v>
       </c>
-      <c r="R21" s="1">
+      <c r="R22" s="1">
         <v>15</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S22" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
@@ -1565,7 +1606,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>34</v>
@@ -1622,8 +1663,67 @@
         <v>8</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -1633,9 +1733,10 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
     <mergeCell ref="C9:S9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C10:S10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1651,7 +1752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1697,7 +1798,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1720,7 +1821,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1793,11 +1894,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1850,11 +1951,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1925,6 +2026,582 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4">
+        <v>11</v>
+      </c>
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1941,56 +2618,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2009,25 +2686,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2050,25 +2727,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2091,25 +2768,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2132,25 +2809,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2173,25 +2850,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2214,25 +2891,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -2255,25 +2932,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2296,25 +2973,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2337,25 +3014,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2378,25 +3055,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2419,25 +3096,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="H14" s="16" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -2460,25 +3137,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -2501,25 +3178,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -2534,6 +3211,170 @@
         <v>8</v>
       </c>
       <c r="M16" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="7" t="s">
         <v>8</v>
       </c>
     </row>
